--- a/golf_scores.xlsx
+++ b/golf_scores.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SKY\PycharmProjects\PythonProject6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\golf score\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF05E55E-A011-4896-96C4-1DEED4248818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF905BF9-F401-4330-85CB-AB85AA8B44B7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{977EBE3A-9F1B-4B6C-B906-0229579FA1E5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>이희수</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -82,6 +82,10 @@
   </si>
   <si>
     <t>5회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6회</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2E98F5-20E4-44ED-99EA-B416938E49A8}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
@@ -683,8 +687,50 @@
         <v>124</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2">
+        <f>72+24</f>
+        <v>96</v>
+      </c>
+      <c r="C7" s="2">
+        <f>72+12</f>
+        <v>84</v>
+      </c>
+      <c r="D7" s="2">
+        <f>72+55</f>
+        <v>127</v>
+      </c>
+      <c r="E7" s="2">
+        <f>72+28</f>
+        <v>100</v>
+      </c>
+      <c r="F7" s="2">
+        <f>72+49</f>
+        <v>121</v>
+      </c>
+      <c r="G7" s="2">
+        <f>72+31</f>
+        <v>103</v>
+      </c>
+      <c r="H7" s="2">
+        <f>72+26</f>
+        <v>98</v>
+      </c>
+      <c r="I7" s="2">
+        <f>72+16</f>
+        <v>88</v>
+      </c>
+      <c r="J7" s="2">
+        <f>72+45</f>
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>